--- a/Fragenliste BINGO.xlsx
+++ b/Fragenliste BINGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcgcloudeur-my.sharepoint.com/personal/wessels_david_bcg_com/Documents/Documents/01_Personal/07_Other/30. Geburtstag/birthday-hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="13_ncr:b_{9FDDD553-8BD7-4C91-8A4E-08E7AA5C7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA385273-4FA2-431F-A26D-173C5EA5EEE8}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:b_{9FDDD553-8BD7-4C91-8A4E-08E7AA5C7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527C9492-E42A-4850-B586-471E8FBC3A00}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{F84C07A2-B8C1-4649-9BC2-A0581D232FA6}"/>
   </bookViews>
@@ -81,12 +81,6 @@
     <t>Schwierigkeit</t>
   </si>
   <si>
-    <t>Mit Bennet oder David studiert</t>
-  </si>
-  <si>
-    <t>Mit Bennet oder David in einem Club / Verein</t>
-  </si>
-  <si>
     <t>Bennet &amp; David</t>
   </si>
   <si>
@@ -96,9 +90,6 @@
     <t>schwer</t>
   </si>
   <si>
-    <t>Mit Bennet oder David im Skiurlaub gewesen</t>
-  </si>
-  <si>
     <t>Wohnt in Berlin</t>
   </si>
   <si>
@@ -120,27 +111,9 @@
     <t>aktiv</t>
   </si>
   <si>
-    <t>Bennet oder David schon mal nackt gesehen</t>
-  </si>
-  <si>
-    <t>Größer als Bennet und David</t>
-  </si>
-  <si>
     <t>leicht</t>
   </si>
   <si>
-    <t>Spricht  eine weitere Fremdsprache neben Englisch</t>
-  </si>
-  <si>
-    <t>Mit Bennet oder David zusammen gearbeiteit</t>
-  </si>
-  <si>
-    <t>Kennt Bennet oder David über 15 Jahre</t>
-  </si>
-  <si>
-    <t>Kennt Bennet oder David weniger als 2 Jahre</t>
-  </si>
-  <si>
     <t>Ist oder wird Lehrer</t>
   </si>
   <si>
@@ -150,36 +123,12 @@
     <t>War in Südamerika</t>
   </si>
   <si>
-    <t>Hat einen BahnBonus Status von Silber oder höher</t>
-  </si>
-  <si>
     <t>Aktivität</t>
   </si>
   <si>
-    <t>Hat mir mir ein Foto gemacht und hochgeladen</t>
-  </si>
-  <si>
-    <t>Person die ich heute erst kennengelernt habe</t>
-  </si>
-  <si>
     <t>War dieses Jahr außerhalb von Europa</t>
   </si>
   <si>
-    <t>Hat schon mal mehr als 5 Monate im Ausland gelebt</t>
-  </si>
-  <si>
-    <t>Mit Bennet oder David in einem Zelt geschlafen</t>
-  </si>
-  <si>
-    <t>Hat  einen Halbmarathon (erfolgreich) beendet</t>
-  </si>
-  <si>
-    <t>Mit Bennet oder David zwischen 6-9 Uhr morgens getrunken</t>
-  </si>
-  <si>
-    <t>Hat gerade einen Drink mit mir geext</t>
-  </si>
-  <si>
     <t>A1</t>
   </si>
   <si>
@@ -307,6 +256,57 @@
   </si>
   <si>
     <t>ja</t>
+  </si>
+  <si>
+    <t>Spricht  eine weitere Fremdsprache</t>
+  </si>
+  <si>
+    <t>Habe ich heute kennengelernt</t>
+  </si>
+  <si>
+    <t>Hat mehr als 5 Monate im Ausland gelebt</t>
+  </si>
+  <si>
+    <t>Hat Halbmarathon beendet</t>
+  </si>
+  <si>
+    <t>Hat  BahnBonus Status Silber oder höher</t>
+  </si>
+  <si>
+    <t>Hat gerade Drink mit mir geext</t>
+  </si>
+  <si>
+    <t>Haben ein Foto in POV gemacht</t>
+  </si>
+  <si>
+    <t>Kennt Bennet / David über 15 Jahre</t>
+  </si>
+  <si>
+    <t>Kennt Bennet / David weniger als 2 Jahre</t>
+  </si>
+  <si>
+    <t>Mit Bennet / David studiert</t>
+  </si>
+  <si>
+    <t>Mit Bennet / David im Skiurlaub gewesen</t>
+  </si>
+  <si>
+    <t>Hat Bennet / David schon nackt gesehen</t>
+  </si>
+  <si>
+    <t>Größer als Bennet &amp; David</t>
+  </si>
+  <si>
+    <t>Mit Bennet / David  gearbeiteit</t>
+  </si>
+  <si>
+    <t>Mit Bennet / David in Club / Verein</t>
+  </si>
+  <si>
+    <t>Mit Bennet / David in  Zelt geschlafen</t>
+  </si>
+  <si>
+    <t>Mit Bennet / David zwischen 6-9 Uhr  getrunken</t>
   </si>
 </sst>
 </file>
@@ -724,7 +724,7 @@
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
     <col min="4" max="4" width="90.5703125" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
@@ -750,10 +750,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -761,28 +761,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K2" s="2"/>
     </row>
@@ -791,28 +791,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K3">
         <f>COUNTIFS($F$1:$F$40,"P")</f>
@@ -824,28 +824,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K4" cm="1">
         <f t="array" ref="K4">SUMPRODUCT((LEN(F2:F40)=2)*ISNUMBER(VALUE(MID(F2:F40&amp;"00",2,1)))/COUNTIF(F2:F40,LEFT(F2:F40,1)&amp;"*"))</f>
@@ -857,28 +857,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="K5">
         <f>COUNTIFS($F$1:$F$40,"S")</f>
@@ -890,22 +890,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -913,22 +913,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -936,22 +936,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -959,22 +959,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -982,22 +982,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1005,22 +1005,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1028,22 +1028,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1051,22 +1051,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1074,22 +1074,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1097,22 +1097,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1120,22 +1120,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
         <v>12</v>
       </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1143,22 +1143,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1166,22 +1166,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1189,22 +1189,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1212,22 +1212,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1235,22 +1235,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1258,22 +1258,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1281,22 +1281,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1304,22 +1304,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1327,22 +1327,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1350,22 +1350,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Fragenliste BINGO.xlsx
+++ b/Fragenliste BINGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcgcloudeur-my.sharepoint.com/personal/wessels_david_bcg_com/Documents/Documents/01_Personal/07_Other/30. Geburtstag/birthday-hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:b_{9FDDD553-8BD7-4C91-8A4E-08E7AA5C7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527C9492-E42A-4850-B586-471E8FBC3A00}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:b_{9FDDD553-8BD7-4C91-8A4E-08E7AA5C7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3B83C19-BEFC-4C68-82E5-AFF29DFF5C4B}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{F84C07A2-B8C1-4649-9BC2-A0581D232FA6}"/>
   </bookViews>
@@ -300,13 +300,13 @@
     <t>Mit Bennet / David  gearbeiteit</t>
   </si>
   <si>
-    <t>Mit Bennet / David in Club / Verein</t>
-  </si>
-  <si>
     <t>Mit Bennet / David in  Zelt geschlafen</t>
   </si>
   <si>
     <t>Mit Bennet / David zwischen 6-9 Uhr  getrunken</t>
+  </si>
+  <si>
+    <t>Mit Bennet / David in Club oder Verein</t>
   </si>
 </sst>
 </file>
@@ -827,7 +827,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
         <v>40</v>
@@ -985,7 +985,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -1008,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
         <v>47</v>

--- a/Fragenliste BINGO.xlsx
+++ b/Fragenliste BINGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcgcloudeur-my.sharepoint.com/personal/wessels_david_bcg_com/Documents/Documents/01_Personal/07_Other/30. Geburtstag/birthday-hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:b_{9FDDD553-8BD7-4C91-8A4E-08E7AA5C7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3B83C19-BEFC-4C68-82E5-AFF29DFF5C4B}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:b_{9FDDD553-8BD7-4C91-8A4E-08E7AA5C7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58311BDB-1AD6-44FA-99D2-E234C65E03F5}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{F84C07A2-B8C1-4649-9BC2-A0581D232FA6}"/>
   </bookViews>
@@ -252,9 +252,6 @@
     <t>Finde jemanden, der/die gerade einen Drink mit dir geext hat.</t>
   </si>
   <si>
-    <t>Finde jemanden, der/die dir gerade ein Foto gemacht und hochgeladen hat.</t>
-  </si>
-  <si>
     <t>ja</t>
   </si>
   <si>
@@ -270,15 +267,6 @@
     <t>Hat Halbmarathon beendet</t>
   </si>
   <si>
-    <t>Hat  BahnBonus Status Silber oder höher</t>
-  </si>
-  <si>
-    <t>Hat gerade Drink mit mir geext</t>
-  </si>
-  <si>
-    <t>Haben ein Foto in POV gemacht</t>
-  </si>
-  <si>
     <t>Kennt Bennet / David über 15 Jahre</t>
   </si>
   <si>
@@ -307,6 +295,18 @@
   </si>
   <si>
     <t>Mit Bennet / David in Club oder Verein</t>
+  </si>
+  <si>
+    <t>Finde jemanden, der/die mit dir gemeinsam ein Foto macht und in unser App-Album hochlädt.</t>
+  </si>
+  <si>
+    <t>Gemeinsames Foto gemacht</t>
+  </si>
+  <si>
+    <t>Drink mit mir gerade geext</t>
+  </si>
+  <si>
+    <t>Hat BahnBonus Status Silber oder höher</t>
   </si>
 </sst>
 </file>
@@ -764,7 +764,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -776,7 +776,7 @@
         <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>26</v>
@@ -794,7 +794,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
@@ -806,7 +806,7 @@
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
         <v>34</v>
@@ -827,7 +827,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
         <v>40</v>
@@ -839,7 +839,7 @@
         <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
         <v>41</v>
@@ -872,7 +872,7 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
         <v>33</v>
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
@@ -905,7 +905,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -916,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
@@ -928,7 +928,7 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -939,7 +939,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
@@ -951,7 +951,7 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -962,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -974,7 +974,7 @@
         <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -985,7 +985,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -997,7 +997,7 @@
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1008,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>47</v>
@@ -1020,7 +1020,7 @@
         <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1043,7 +1043,7 @@
         <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1054,7 +1054,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>49</v>
@@ -1066,7 +1066,7 @@
         <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1089,7 +1089,7 @@
         <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1112,7 +1112,7 @@
         <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1135,7 +1135,7 @@
         <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1158,7 +1158,7 @@
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
@@ -1181,7 +1181,7 @@
         <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
@@ -1204,7 +1204,7 @@
         <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -1227,7 +1227,7 @@
         <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1250,7 +1250,7 @@
         <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1273,7 +1273,7 @@
         <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
         <v>59</v>
@@ -1296,7 +1296,7 @@
         <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1319,7 +1319,7 @@
         <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1330,7 +1330,7 @@
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
         <v>61</v>
@@ -1342,7 +1342,7 @@
         <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1353,10 +1353,10 @@
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -1365,7 +1365,7 @@
         <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
